--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepRelDeal.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepRelDeal.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\yunying\nanying\code-01\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19460" windowHeight="7710"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19455" windowHeight="7710"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,12 +23,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>生效日（yyyy-mm-dd）*</t>
-  </si>
-  <si>
-    <t>生效截止日期（yyyy-mm-dd）*</t>
-  </si>
-  <si>
     <t>投资于关联方承销的证券交易金额*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -58,6 +52,14 @@
   </si>
   <si>
     <t>投资于关联方发行的证券、关联方作为融资人的非标准化债权类资产业务交易金额*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生效日（yyyy/mm/dd）*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生效截止日期（yyyy/mm/dd）*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -432,41 +434,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultColWidth="15.36328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.375" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="9" max="10" width="15.36328125" style="4"/>
+    <col min="9" max="9" width="15.5" style="4" customWidth="1"/>
+    <col min="10" max="10" width="15.375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" ht="84" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="81" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -479,7 +482,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -490,7 +493,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepRelDeal.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepRelDeal.xlsx
@@ -123,10 +123,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepRelDeal.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepRelDeal.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25629"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C753657-8FD4-49C7-A314-BD51AD91AF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19455" windowHeight="7710"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -66,7 +67,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -113,7 +117,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -127,6 +131,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -432,37 +442,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultColWidth="15.375" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="15.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="9" max="9" width="15.5" style="4" customWidth="1"/>
-    <col min="10" max="10" width="15.375" style="4"/>
+    <col min="2" max="8" width="15.33203125" style="6"/>
+    <col min="9" max="9" width="15.44140625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" ht="81" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
@@ -480,9 +491,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -491,9 +502,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepRelDeal.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepRelDeal.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C753657-8FD4-49C7-A314-BD51AD91AF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44CC5BD-F7DC-4C98-A9A3-0F64304E76E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,9 +68,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
-  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -133,10 +130,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
